--- a/EXPOSICIÓN/Cronograma_V8.xlsx
+++ b/EXPOSICIÓN/Cronograma_V8.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Universidad\Tercer Semestre\Metodología De Desarrollo Software\FInal\Subir ya a git hub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE01CE07-02EA-41D7-89DD-76EB0A01F69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418F7FC0-77ED-4CEC-A2B2-E3FDEC1121C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{292D496C-6FD7-5443-935C-6D6B92A280D5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="62">
   <si>
     <t>Estado</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>ALEJANDRO DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ALEJANDRO DE LA CRUZ IAN ESCOBAR SANTIAGO NOGALES</t>
   </si>
   <si>
     <t>IAN ESCOBAR</t>
@@ -749,7 +746,7 @@
         <v>15</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D8" s="9">
         <v>45775</v>
@@ -758,7 +755,7 @@
         <v>45777</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -778,7 +775,7 @@
         <v>45775</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -809,7 +806,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D11" s="9">
         <v>45783</v>
@@ -838,7 +835,7 @@
         <v>45786</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -849,7 +846,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D13" s="9">
         <v>45785</v>
@@ -858,7 +855,7 @@
         <v>45786</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -869,7 +866,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="9">
         <v>45787</v>
@@ -889,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D15" s="9">
         <v>45788</v>
@@ -918,7 +915,7 @@
         <v>45790</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -929,7 +926,7 @@
         <v>18</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D17" s="9">
         <v>45791</v>
@@ -938,7 +935,7 @@
         <v>45792</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -949,7 +946,7 @@
         <v>19</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D18" s="9">
         <v>45792</v>
@@ -958,7 +955,7 @@
         <v>45793</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -969,7 +966,7 @@
         <v>20</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D19" s="8">
         <v>45793</v>
@@ -978,7 +975,7 @@
         <v>45794</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -989,7 +986,7 @@
         <v>21</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="9">
         <v>45794</v>
@@ -998,7 +995,7 @@
         <v>45795</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -1038,7 +1035,7 @@
         <v>45798</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="21" x14ac:dyDescent="0.35">
@@ -1046,7 +1043,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>14</v>
@@ -1066,10 +1063,10 @@
         <v>17</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24" s="12">
         <v>45800</v>
@@ -1086,10 +1083,10 @@
         <v>17</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D25" s="12">
         <v>45803</v>
@@ -1098,7 +1095,7 @@
         <v>45805</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1106,10 +1103,10 @@
         <v>17</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D26" s="12">
         <v>45806</v>
@@ -1118,7 +1115,7 @@
         <v>45808</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1126,10 +1123,10 @@
         <v>17</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D27" s="12">
         <v>45809</v>
@@ -1146,10 +1143,10 @@
         <v>17</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D28" s="12">
         <v>45812</v>
@@ -1158,7 +1155,7 @@
         <v>45813</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1166,10 +1163,10 @@
         <v>17</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29" s="12">
         <v>45813</v>
@@ -1178,7 +1175,7 @@
         <v>45814</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1186,10 +1183,10 @@
         <v>17</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D30" s="12">
         <v>45814</v>
@@ -1198,7 +1195,7 @@
         <v>45815</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1206,10 +1203,10 @@
         <v>17</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="12">
         <v>45815</v>
@@ -1218,7 +1215,7 @@
         <v>45816</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1226,19 +1223,19 @@
         <v>17</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E32" s="12">
         <v>45819</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1246,10 +1243,10 @@
         <v>17</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D33" s="12">
         <v>45819</v>
@@ -1266,10 +1263,10 @@
         <v>17</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D34" s="12">
         <v>45820</v>
@@ -1278,7 +1275,7 @@
         <v>45821</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1286,10 +1283,10 @@
         <v>17</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" s="12">
         <v>45821</v>
@@ -1306,7 +1303,7 @@
         <v>17</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>9</v>
@@ -1318,7 +1315,7 @@
         <v>45823</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1326,10 +1323,10 @@
         <v>17</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D37" s="12">
         <v>45852</v>
@@ -1338,7 +1335,7 @@
         <v>45853</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1346,10 +1343,10 @@
         <v>17</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D38" s="12">
         <v>45853</v>
@@ -1358,7 +1355,7 @@
         <v>45853</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1366,10 +1363,10 @@
         <v>17</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D39" s="12">
         <v>45851</v>
@@ -1378,7 +1375,7 @@
         <v>45851</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1386,10 +1383,10 @@
         <v>17</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D40" s="12">
         <v>45852</v>
@@ -1398,7 +1395,7 @@
         <v>45852</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1406,10 +1403,10 @@
         <v>17</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D41" s="12">
         <v>45852</v>
@@ -1426,10 +1423,10 @@
         <v>17</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D42" s="12">
         <v>45863</v>
@@ -1438,7 +1435,7 @@
         <v>45863</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1446,10 +1443,10 @@
         <v>17</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D43" s="12">
         <v>45863</v>
@@ -1458,7 +1455,7 @@
         <v>45863</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1466,10 +1463,10 @@
         <v>17</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D44" s="12">
         <v>45872</v>
@@ -1478,7 +1475,7 @@
         <v>45872</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1486,10 +1483,10 @@
         <v>17</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D45" s="12">
         <v>45872</v>
@@ -1498,7 +1495,7 @@
         <v>45872</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1506,10 +1503,10 @@
         <v>17</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D46" s="12">
         <v>45872</v>
@@ -1526,10 +1523,10 @@
         <v>17</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D47" s="12">
         <v>45872</v>
@@ -1538,7 +1535,7 @@
         <v>45872</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
@@ -1546,10 +1543,10 @@
         <v>17</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D48" s="12">
         <v>45873</v>
@@ -1558,7 +1555,7 @@
         <v>45873</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1566,5 +1563,6 @@
     <mergeCell ref="A4:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
 </worksheet>
 </file>